--- a/data/dividends_info_20260325.xlsx
+++ b/data/dividends_info_20260325.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>49.97999954223633</v>
+        <v>50.95000076293945</v>
       </c>
       <c r="I2" t="n">
-        <v>1.400560236917279</v>
+        <v>1.373895955874398</v>
       </c>
       <c r="J2" t="n">
         <v>334</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.952000021934509</v>
+        <v>1.985999941825867</v>
       </c>
       <c r="I3" t="n">
-        <v>3.944672086821493</v>
+        <v>3.877140093428633</v>
       </c>
       <c r="J3" t="n">
         <v>243</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5.400000095367432</v>
+        <v>5.409999847412109</v>
       </c>
       <c r="I4" t="n">
-        <v>3.703703638293944</v>
+        <v>3.696857775248748</v>
       </c>
       <c r="J4" t="n">
         <v>236</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9.208000183105469</v>
+        <v>9.295000076293945</v>
       </c>
       <c r="I5" t="n">
-        <v>2.823631568524937</v>
+        <v>2.797202774243181</v>
       </c>
       <c r="J5" t="n">
         <v>117</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>4.429999828338623</v>
+        <v>4.795000076293945</v>
       </c>
       <c r="I7" t="n">
-        <v>2.708803716703606</v>
+        <v>2.502606842349583</v>
       </c>
       <c r="J7" t="n">
         <v>110</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.099999904632568</v>
+        <v>2.119999885559082</v>
       </c>
       <c r="I8" t="n">
-        <v>4.047619231433834</v>
+        <v>4.009434178699683</v>
       </c>
       <c r="J8" t="n">
         <v>103</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30.20000076293945</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4966887291740587</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>103</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>21.8799991607666</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="I10" t="n">
-        <v>1.142596021887785</v>
+        <v>1.121076271538714</v>
       </c>
       <c r="J10" t="n">
         <v>89</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>20.60000038146973</v>
+        <v>21.45000076293945</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9466019242184478</v>
+        <v>0.9090908767561168</v>
       </c>
       <c r="J11" t="n">
         <v>89</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.179999828338623</v>
+        <v>5.139999866485596</v>
       </c>
       <c r="I12" t="n">
-        <v>5.59845578398429</v>
+        <v>5.642023492858249</v>
       </c>
       <c r="J12" t="n">
         <v>89</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2.380000114440918</v>
+        <v>2.441999912261963</v>
       </c>
       <c r="I13" t="n">
-        <v>5.823529131743689</v>
+        <v>5.675675879595684</v>
       </c>
       <c r="J13" t="n">
         <v>89</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>57.97999954223633</v>
+        <v>59.02000045776367</v>
       </c>
       <c r="I14" t="n">
-        <v>1.086581588433901</v>
+        <v>1.06743475959619</v>
       </c>
       <c r="J14" t="n">
         <v>89</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>15.94999980926514</v>
+        <v>16.54999923706055</v>
       </c>
       <c r="I15" t="n">
-        <v>4.890282190140897</v>
+        <v>4.712991153820356</v>
       </c>
       <c r="J15" t="n">
         <v>89</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>19.92000007629395</v>
+        <v>20.07999992370605</v>
       </c>
       <c r="I16" t="n">
-        <v>4.267068256749424</v>
+        <v>4.233067745167203</v>
       </c>
       <c r="J16" t="n">
         <v>89</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6.315999984741211</v>
+        <v>6.349999904632568</v>
       </c>
       <c r="I17" t="n">
-        <v>2.870487657346448</v>
+        <v>2.855118153115793</v>
       </c>
       <c r="J17" t="n">
         <v>89</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>7.550000190734863</v>
+        <v>7.739999771118164</v>
       </c>
       <c r="I18" t="n">
-        <v>3.443708522273474</v>
+        <v>3.359173225950095</v>
       </c>
       <c r="J18" t="n">
         <v>89</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.8270000219345093</v>
+        <v>0.8379999995231628</v>
       </c>
       <c r="I20" t="n">
-        <v>3.627569432201989</v>
+        <v>3.57995226934016</v>
       </c>
       <c r="J20" t="n">
         <v>68</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.4679999947547913</v>
+        <v>0.4720000028610229</v>
       </c>
       <c r="I21" t="n">
-        <v>4.914529969610546</v>
+        <v>4.872881326395285</v>
       </c>
       <c r="J21" t="n">
         <v>68</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.575000047683716</v>
+        <v>2.549999952316284</v>
       </c>
       <c r="I22" t="n">
-        <v>6.990291132690076</v>
+        <v>7.058823661408212</v>
       </c>
       <c r="J22" t="n">
         <v>61</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>11.86999988555908</v>
+        <v>12.22000026702881</v>
       </c>
       <c r="I23" t="n">
-        <v>2.106149978182791</v>
+        <v>2.045826469206661</v>
       </c>
       <c r="J23" t="n">
         <v>61</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>3.519999980926514</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="I24" t="n">
-        <v>4.261363659454279</v>
+        <v>4.189944223370775</v>
       </c>
       <c r="J24" t="n">
         <v>61</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13</v>
+        <v>13.60000038146973</v>
       </c>
       <c r="I25" t="n">
-        <v>4.461538461538462</v>
+        <v>4.264705762731166</v>
       </c>
       <c r="J25" t="n">
         <v>61</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2.348000049591064</v>
+        <v>2.377000093460083</v>
       </c>
       <c r="I26" t="n">
-        <v>4.429301439670454</v>
+        <v>4.375262764445763</v>
       </c>
       <c r="J26" t="n">
         <v>54</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>8.744000434875488</v>
+        <v>8.887999534606934</v>
       </c>
       <c r="I27" t="n">
-        <v>3.316559761860642</v>
+        <v>3.262826453476238</v>
       </c>
       <c r="J27" t="n">
         <v>54</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1.952000021934509</v>
+        <v>1.985999941825867</v>
       </c>
       <c r="I28" t="n">
-        <v>3.944672086821493</v>
+        <v>3.877140093428633</v>
       </c>
       <c r="J28" t="n">
         <v>54</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>33.2599983215332</v>
+        <v>33.83000183105469</v>
       </c>
       <c r="I29" t="n">
-        <v>4.930848114139051</v>
+        <v>4.847767990643562</v>
       </c>
       <c r="J29" t="n">
         <v>54</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>32.36999893188477</v>
+        <v>32.93999862670898</v>
       </c>
       <c r="I30" t="n">
-        <v>6.178560599302277</v>
+        <v>6.071645669038751</v>
       </c>
       <c r="J30" t="n">
         <v>54</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3.742000102996826</v>
+        <v>3.769999980926514</v>
       </c>
       <c r="I31" t="n">
-        <v>2.672367644242281</v>
+        <v>2.652519907319046</v>
       </c>
       <c r="J31" t="n">
         <v>54</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>33.09999847412109</v>
+        <v>34.79999923706055</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4485196581385705</v>
+        <v>0.4266092047550861</v>
       </c>
       <c r="J32" t="n">
         <v>54</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>21.95999908447266</v>
+        <v>22.42000007629395</v>
       </c>
       <c r="I33" t="n">
-        <v>4.189435511636738</v>
+        <v>4.103479022610588</v>
       </c>
       <c r="J33" t="n">
         <v>54</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>7.764999866485596</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I34" t="n">
-        <v>3.863490085747788</v>
+        <v>3.703703529277682</v>
       </c>
       <c r="J34" t="n">
         <v>54</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>72.83999633789062</v>
+        <v>73.30000305175781</v>
       </c>
       <c r="I35" t="n">
-        <v>1.427787002041628</v>
+        <v>1.418826680355861</v>
       </c>
       <c r="J35" t="n">
         <v>54</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>49.97999954223633</v>
+        <v>50.95000076293945</v>
       </c>
       <c r="I36" t="n">
-        <v>4.401760744597162</v>
+        <v>4.317958718462394</v>
       </c>
       <c r="J36" t="n">
         <v>54</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>7.342999935150146</v>
+        <v>7.585999965667725</v>
       </c>
       <c r="I37" t="n">
-        <v>11.71183450354225</v>
+        <v>11.33667286965644</v>
       </c>
       <c r="J37" t="n">
         <v>54</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>10.85999965667725</v>
+        <v>11.14999961853027</v>
       </c>
       <c r="I38" t="n">
-        <v>5.156537916239117</v>
+        <v>5.022421696493439</v>
       </c>
       <c r="J38" t="n">
         <v>54</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.754999995231628</v>
+        <v>1.769999980926514</v>
       </c>
       <c r="I39" t="n">
-        <v>2.279202285394919</v>
+        <v>2.259887030002217</v>
       </c>
       <c r="J39" t="n">
         <v>54</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>8.619999885559082</v>
+        <v>8.859999656677246</v>
       </c>
       <c r="I40" t="n">
-        <v>3.480278468478685</v>
+        <v>3.386004645879507</v>
       </c>
       <c r="J40" t="n">
         <v>54</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.269999980926514</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I41" t="n">
-        <v>4.757709291077578</v>
+        <v>4.778761082112308</v>
       </c>
       <c r="J41" t="n">
         <v>54</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>61.09999847412109</v>
+        <v>62</v>
       </c>
       <c r="I42" t="n">
-        <v>3.371522179124952</v>
+        <v>3.32258064516129</v>
       </c>
       <c r="J42" t="n">
         <v>54</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>14.19999980926514</v>
+        <v>14.5</v>
       </c>
       <c r="I43" t="n">
-        <v>5.281690211788906</v>
+        <v>5.172413793103448</v>
       </c>
       <c r="J43" t="n">
         <v>54</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>15.23999977111816</v>
+        <v>15.34000015258789</v>
       </c>
       <c r="I44" t="n">
-        <v>1.968503966571837</v>
+        <v>1.955671427743691</v>
       </c>
       <c r="J44" t="n">
         <v>54</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>41</v>
+        <v>40.29999923706055</v>
       </c>
       <c r="I45" t="n">
-        <v>2.073170731707317</v>
+        <v>2.109181181369169</v>
       </c>
       <c r="J45" t="n">
         <v>54</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>29.52000045776367</v>
+        <v>29.92000007629395</v>
       </c>
       <c r="I46" t="n">
-        <v>2.879403749387316</v>
+        <v>2.840909083664968</v>
       </c>
       <c r="J46" t="n">
         <v>54</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>58.29999923706055</v>
+        <v>59.91999816894531</v>
       </c>
       <c r="I47" t="n">
-        <v>2.229845655252783</v>
+        <v>2.169559478848165</v>
       </c>
       <c r="J47" t="n">
         <v>54</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5.400000095367432</v>
+        <v>5.409999847412109</v>
       </c>
       <c r="I48" t="n">
-        <v>3.703703638293944</v>
+        <v>3.696857775248748</v>
       </c>
       <c r="J48" t="n">
         <v>54</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>20.6200008392334</v>
+        <v>21.29999923706055</v>
       </c>
       <c r="I49" t="n">
-        <v>4.849660326382303</v>
+        <v>4.694835848914343</v>
       </c>
       <c r="J49" t="n">
         <v>54</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>4.239999771118164</v>
+        <v>4.28000020980835</v>
       </c>
       <c r="I50" t="n">
-        <v>5.070754990708423</v>
+        <v>5.023364239732766</v>
       </c>
       <c r="J50" t="n">
         <v>54</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>8.939999580383301</v>
+        <v>9.079999923706055</v>
       </c>
       <c r="I51" t="n">
-        <v>2.684563884394612</v>
+        <v>2.643171828376432</v>
       </c>
       <c r="J51" t="n">
         <v>54</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>18.79500007629395</v>
+        <v>19.125</v>
       </c>
       <c r="I52" t="n">
-        <v>4.203245526965566</v>
+        <v>4.130718954248366</v>
       </c>
       <c r="J52" t="n">
         <v>54</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>4.610000133514404</v>
+        <v>4.454999923706055</v>
       </c>
       <c r="I53" t="n">
-        <v>2.017353520749294</v>
+        <v>2.087542123292216</v>
       </c>
       <c r="J53" t="n">
         <v>54</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>32</v>
+        <v>33.40000152587891</v>
       </c>
       <c r="I54" t="n">
-        <v>1.09375</v>
+        <v>1.047904143743269</v>
       </c>
       <c r="J54" t="n">
         <v>54</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1.945000052452087</v>
+        <v>1.970000028610229</v>
       </c>
       <c r="I55" t="n">
-        <v>3.084832821693614</v>
+        <v>3.045685234955455</v>
       </c>
       <c r="J55" t="n">
         <v>54</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>11.30000019073486</v>
+        <v>11.85000038146973</v>
       </c>
       <c r="I56" t="n">
-        <v>1.769911474550104</v>
+        <v>1.687763658748461</v>
       </c>
       <c r="J56" t="n">
         <v>54</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>5.650000095367432</v>
+        <v>5.730000019073486</v>
       </c>
       <c r="I57" t="n">
-        <v>1.823008818786607</v>
+        <v>1.797556713039149</v>
       </c>
       <c r="J57" t="n">
         <v>54</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>5.085000038146973</v>
+        <v>5.166999816894531</v>
       </c>
       <c r="I58" t="n">
-        <v>3.736479814643974</v>
+        <v>3.677182247592835</v>
       </c>
       <c r="J58" t="n">
         <v>54</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>9.824999809265137</v>
+        <v>9.954999923706055</v>
       </c>
       <c r="I59" t="n">
-        <v>4.396946650244379</v>
+        <v>4.339527908697107</v>
       </c>
       <c r="J59" t="n">
         <v>54</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>25.1200008392334</v>
+        <v>25.89999961853027</v>
       </c>
       <c r="I60" t="n">
-        <v>1.751592298168999</v>
+        <v>1.698841723863193</v>
       </c>
       <c r="J60" t="n">
         <v>54</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>6.920000076293945</v>
+        <v>7.119999885559082</v>
       </c>
       <c r="I61" t="n">
-        <v>6.791907439569159</v>
+        <v>6.601123701606553</v>
       </c>
       <c r="J61" t="n">
         <v>54</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>52.29999923706055</v>
+        <v>52.11999893188477</v>
       </c>
       <c r="I62" t="n">
-        <v>2.676864283791307</v>
+        <v>2.686109034326055</v>
       </c>
       <c r="J62" t="n">
         <v>54</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2.967999935150146</v>
+        <v>3.055000066757202</v>
       </c>
       <c r="I63" t="n">
-        <v>10.10781693244287</v>
+        <v>9.819967052191972</v>
       </c>
       <c r="J63" t="n">
         <v>54</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>3.109999895095825</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="I65" t="n">
-        <v>1.125401967221661</v>
+        <v>1.132686115604929</v>
       </c>
       <c r="J65" t="n">
         <v>54</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>5.869999885559082</v>
+        <v>5.829999923706055</v>
       </c>
       <c r="I66" t="n">
-        <v>5.621805901765695</v>
+        <v>5.660377432564756</v>
       </c>
       <c r="J66" t="n">
         <v>54</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.9399999976158142</v>
+        <v>0.9340000152587891</v>
       </c>
       <c r="I67" t="n">
-        <v>7.446808529526145</v>
+        <v>7.494646558501896</v>
       </c>
       <c r="J67" t="n">
         <v>54</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>45.54000091552734</v>
+        <v>46.27999877929688</v>
       </c>
       <c r="I68" t="n">
-        <v>1.559068919030078</v>
+        <v>1.534140057751287</v>
       </c>
       <c r="J68" t="n">
         <v>54</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>77.15000152587891</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="I69" t="n">
-        <v>1.749837943356568</v>
+        <v>1.715374907686262</v>
       </c>
       <c r="J69" t="n">
         <v>54</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>3.586999893188477</v>
+        <v>3.604000091552734</v>
       </c>
       <c r="I70" t="n">
-        <v>4.739336634016104</v>
+        <v>4.716981012249581</v>
       </c>
       <c r="J70" t="n">
         <v>54</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>4.920000076293945</v>
+        <v>4.760000228881836</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8130081174740657</v>
+        <v>0.8403360940467085</v>
       </c>
       <c r="J71" t="n">
         <v>54</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>30.14999961853027</v>
+        <v>30.95000076293945</v>
       </c>
       <c r="I72" t="n">
-        <v>3.482587108739687</v>
+        <v>3.392568575498404</v>
       </c>
       <c r="J72" t="n">
         <v>54</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>17.29999923706055</v>
+        <v>17.36000061035156</v>
       </c>
       <c r="I73" t="n">
-        <v>2.196531888775771</v>
+        <v>2.188940015206051</v>
       </c>
       <c r="J73" t="n">
         <v>54</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>24.89999961853027</v>
+        <v>24.71999931335449</v>
       </c>
       <c r="I74" t="n">
-        <v>2.409638591132698</v>
+        <v>2.427184533439132</v>
       </c>
       <c r="J74" t="n">
         <v>54</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>29.25</v>
+        <v>28.54999923706055</v>
       </c>
       <c r="I75" t="n">
-        <v>1.196581196581197</v>
+        <v>1.225919472339837</v>
       </c>
       <c r="J75" t="n">
         <v>54</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>2.302000045776367</v>
+        <v>2.348000049591064</v>
       </c>
       <c r="I76" t="n">
-        <v>11.29452627409975</v>
+        <v>11.07325359917614</v>
       </c>
       <c r="J76" t="n">
         <v>54</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>9.199999809265137</v>
+        <v>9.300000190734863</v>
       </c>
       <c r="I77" t="n">
-        <v>3.804347904958889</v>
+        <v>3.763440783030176</v>
       </c>
       <c r="J77" t="n">
         <v>47</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>4.659999847412109</v>
+        <v>4.760000228881836</v>
       </c>
       <c r="I78" t="n">
-        <v>2.0600859043657</v>
+        <v>2.0168066257121</v>
       </c>
       <c r="J78" t="n">
         <v>47</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>14.23999977111816</v>
+        <v>14.46000003814697</v>
       </c>
       <c r="I79" t="n">
-        <v>3.511236011492847</v>
+        <v>3.457814652012091</v>
       </c>
       <c r="J79" t="n">
         <v>47</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>6.679999828338623</v>
+        <v>6.909999847412109</v>
       </c>
       <c r="I80" t="n">
-        <v>3.293413258286205</v>
+        <v>3.183791676672656</v>
       </c>
       <c r="J80" t="n">
         <v>47</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>3.375</v>
+        <v>3.460000038146973</v>
       </c>
       <c r="I81" t="n">
-        <v>4.74074074074074</v>
+        <v>4.624277405664109</v>
       </c>
       <c r="J81" t="n">
         <v>40</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>18.6200008392334</v>
+        <v>19.04000091552734</v>
       </c>
       <c r="I82" t="n">
-        <v>3.276047113352946</v>
+        <v>3.203781358553075</v>
       </c>
       <c r="J82" t="n">
         <v>40</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>12.19999980926514</v>
+        <v>12.05000019073486</v>
       </c>
       <c r="I83" t="n">
-        <v>5.737705007736096</v>
+        <v>5.809128538754909</v>
       </c>
       <c r="J83" t="n">
         <v>40</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>8.630000114440918</v>
+        <v>8.680000305175781</v>
       </c>
       <c r="I84" t="n">
-        <v>5.915411277292573</v>
+        <v>5.881336198750994</v>
       </c>
       <c r="J84" t="n">
         <v>40</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>7.71999979019165</v>
+        <v>7.400000095367432</v>
       </c>
       <c r="I85" t="n">
-        <v>3.497409421474831</v>
+        <v>3.648648601626724</v>
       </c>
       <c r="J85" t="n">
         <v>40</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>4.800000190734863</v>
+        <v>5.059999942779541</v>
       </c>
       <c r="I86" t="n">
-        <v>7.291666376921876</v>
+        <v>6.916996125650927</v>
       </c>
       <c r="J86" t="n">
         <v>40</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>37.59999847412109</v>
+        <v>38</v>
       </c>
       <c r="I87" t="n">
-        <v>2.925532033617224</v>
+        <v>2.894736842105263</v>
       </c>
       <c r="J87" t="n">
         <v>40</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>18.5</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="I88" t="n">
-        <v>4.054054054054054</v>
+        <v>4.032257981818046</v>
       </c>
       <c r="J88" t="n">
         <v>40</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>9.880000114440918</v>
+        <v>10.10000038146973</v>
       </c>
       <c r="I89" t="n">
-        <v>4.352226670235545</v>
+        <v>4.257425581774359</v>
       </c>
       <c r="J89" t="n">
         <v>40</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>3.980000019073486</v>
+        <v>3.960000038146973</v>
       </c>
       <c r="I90" t="n">
-        <v>3.76884420304397</v>
+        <v>3.787878751389872</v>
       </c>
       <c r="J90" t="n">
         <v>40</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>11.84000015258789</v>
+        <v>12.02000045776367</v>
       </c>
       <c r="I91" t="n">
-        <v>1.665278694754952</v>
+        <v>1.640341035699789</v>
       </c>
       <c r="J91" t="n">
         <v>40</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>25.64999961853027</v>
+        <v>26.35000038146973</v>
       </c>
       <c r="I92" t="n">
-        <v>4.288499089120179</v>
+        <v>4.174572994593047</v>
       </c>
       <c r="J92" t="n">
         <v>40</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>37.25</v>
+        <v>37.75</v>
       </c>
       <c r="I93" t="n">
-        <v>1.261744966442953</v>
+        <v>1.245033112582781</v>
       </c>
       <c r="J93" t="n">
         <v>40</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>75.80000305175781</v>
+        <v>75.90000152587891</v>
       </c>
       <c r="I94" t="n">
-        <v>1.583113392727194</v>
+        <v>1.581027636199516</v>
       </c>
       <c r="J94" t="n">
         <v>40</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>22.85000038146973</v>
+        <v>22.5</v>
       </c>
       <c r="I95" t="n">
-        <v>1.181619236290942</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>40</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>10.25</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I96" t="n">
-        <v>3.707317073170731</v>
+        <v>3.689320320030873</v>
       </c>
       <c r="J96" t="n">
         <v>40</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>27.20000076293945</v>
+        <v>26.70000076293945</v>
       </c>
       <c r="I97" t="n">
-        <v>1.102941145533922</v>
+        <v>1.123595473511786</v>
       </c>
       <c r="J97" t="n">
         <v>40</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>0.153999999165535</v>
+        <v>0.1550000011920929</v>
       </c>
       <c r="I98" t="n">
-        <v>4.545454570084565</v>
+        <v>4.516128997524869</v>
       </c>
       <c r="J98" t="n">
         <v>33</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>6.059999942779541</v>
+        <v>6.539999961853027</v>
       </c>
       <c r="I99" t="n">
-        <v>2.640264051332858</v>
+        <v>2.446483194698154</v>
       </c>
       <c r="J99" t="n">
         <v>33</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>2.154999971389771</v>
+        <v>2.174999952316284</v>
       </c>
       <c r="I100" t="n">
-        <v>3.016241339348193</v>
+        <v>2.988505812645086</v>
       </c>
       <c r="J100" t="n">
         <v>33</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>7.429999828338623</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="I101" t="n">
-        <v>3.364737628209353</v>
+        <v>3.311258194493725</v>
       </c>
       <c r="J101" t="n">
         <v>33</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>6.550000190734863</v>
+        <v>6.670000076293945</v>
       </c>
       <c r="I103" t="n">
-        <v>7.633587563970797</v>
+        <v>7.496251788318048</v>
       </c>
       <c r="J103" t="n">
         <v>26</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>16.67000007629395</v>
+        <v>17.07999992370605</v>
       </c>
       <c r="I104" t="n">
-        <v>3.899220138123162</v>
+        <v>3.805620625898467</v>
       </c>
       <c r="J104" t="n">
         <v>26</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>11.65499973297119</v>
+        <v>12.00500011444092</v>
       </c>
       <c r="I105" t="n">
-        <v>4.633204739356426</v>
+        <v>4.498125738045012</v>
       </c>
       <c r="J105" t="n">
         <v>26</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>6.010000228881836</v>
+        <v>6.105999946594238</v>
       </c>
       <c r="I106" t="n">
-        <v>1.663893447448422</v>
+        <v>1.63773339133056</v>
       </c>
       <c r="J106" t="n">
         <v>26</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>8.159999847412109</v>
+        <v>8.340000152587891</v>
       </c>
       <c r="I107" t="n">
-        <v>1.96078435039117</v>
+        <v>1.918465192717679</v>
       </c>
       <c r="J107" t="n">
         <v>26</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>279.2999877929688</v>
+        <v>276.3999938964844</v>
       </c>
       <c r="I108" t="n">
-        <v>1.294307253131576</v>
+        <v>1.307887148996779</v>
       </c>
       <c r="J108" t="n">
         <v>26</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>25.5</v>
+        <v>26.70000076293945</v>
       </c>
       <c r="I109" t="n">
-        <v>5.333333333333334</v>
+        <v>5.09363281325343</v>
       </c>
       <c r="J109" t="n">
         <v>26</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>12.64999961853027</v>
+        <v>13.42000007629395</v>
       </c>
       <c r="I110" t="n">
-        <v>4.624506068309016</v>
+        <v>4.359165399956935</v>
       </c>
       <c r="J110" t="n">
         <v>26</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>16.34499931335449</v>
+        <v>16.84000015258789</v>
       </c>
       <c r="I111" t="n">
-        <v>3.854389883548455</v>
+        <v>3.741092602681388</v>
       </c>
       <c r="J111" t="n">
         <v>26</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>94.81999969482422</v>
+        <v>98.41999816894531</v>
       </c>
       <c r="I112" t="n">
-        <v>0.9491668454931738</v>
+        <v>0.914448299882187</v>
       </c>
       <c r="J112" t="n">
         <v>26</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>61.52999877929688</v>
+        <v>62.40999984741211</v>
       </c>
       <c r="I113" t="n">
-        <v>2.796684599608673</v>
+        <v>2.75725044737579</v>
       </c>
       <c r="J113" t="n">
         <v>26</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>23.39999961853027</v>
+        <v>23.89999961853027</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5982906080440067</v>
+        <v>0.5857740679269906</v>
       </c>
       <c r="J114" t="n">
         <v>19</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1.929999947547913</v>
+        <v>1.980000019073486</v>
       </c>
       <c r="I116" t="n">
-        <v>1.7616580789651</v>
+        <v>1.717171700630076</v>
       </c>
       <c r="J116" t="n">
         <v>5</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>22.96999931335449</v>
+        <v>23.18000030517578</v>
       </c>
       <c r="I117" t="n">
-        <v>1.131911222343133</v>
+        <v>1.121656585750543</v>
       </c>
       <c r="J117" t="n">
         <v>-2</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>27.51000022888184</v>
+        <v>28.7450008392334</v>
       </c>
       <c r="I118" t="n">
-        <v>0.327153759546363</v>
+        <v>0.31309792093365</v>
       </c>
       <c r="J118" t="n">
         <v>-2</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>49.97999954223633</v>
+        <v>50.95000076293945</v>
       </c>
       <c r="I119" t="n">
-        <v>1.300520219994616</v>
+        <v>1.275760530454798</v>
       </c>
       <c r="J119" t="n">
         <v>-30</v>
@@ -6442,7 +6442,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6459,7 +6459,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -6945,14 +6945,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6969,7 +6969,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6986,7 +6986,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6996,14 +6996,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7013,14 +7013,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7037,7 +7037,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7054,7 +7054,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7064,14 +7064,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7088,7 +7088,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7098,14 +7098,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7122,7 +7122,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7132,14 +7132,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7149,14 +7149,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7173,7 +7173,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7190,7 +7190,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7200,14 +7200,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7251,14 +7251,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7394,7 +7394,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7411,7 +7411,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7428,7 +7428,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7445,7 +7445,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7462,7 +7462,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7581,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7598,7 +7598,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -7615,7 +7615,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7632,7 +7632,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7649,7 +7649,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7683,7 +7683,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7700,7 +7700,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7710,14 +7710,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7734,7 +7734,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7751,7 +7751,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7768,7 +7768,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7785,7 +7785,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7802,7 +7802,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7853,7 +7853,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -7870,7 +7870,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7938,7 +7938,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7955,7 +7955,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7989,7 +7989,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8006,7 +8006,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8023,7 +8023,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8040,7 +8040,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8057,7 +8057,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8074,7 +8074,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8091,7 +8091,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8108,7 +8108,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8125,7 +8125,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8135,14 +8135,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8159,7 +8159,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8176,7 +8176,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8193,7 +8193,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8210,7 +8210,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8227,7 +8227,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8244,7 +8244,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8261,7 +8261,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8278,7 +8278,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8288,14 +8288,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8312,7 +8312,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8329,7 +8329,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8346,7 +8346,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8363,7 +8363,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8380,7 +8380,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8397,7 +8397,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8407,14 +8407,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8431,7 +8431,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -8448,7 +8448,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -8465,7 +8465,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -8475,14 +8475,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -8492,14 +8492,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -8516,7 +8516,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -8526,14 +8526,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -8567,7 +8567,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -8584,7 +8584,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -8601,7 +8601,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -8618,7 +8618,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -8635,7 +8635,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -8652,7 +8652,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -8669,7 +8669,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -8679,14 +8679,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -8703,7 +8703,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -8720,7 +8720,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -8737,7 +8737,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -8754,7 +8754,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -8771,7 +8771,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -8788,7 +8788,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -8798,14 +8798,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -8822,7 +8822,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -8839,7 +8839,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -8849,14 +8849,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -8873,7 +8873,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -8890,7 +8890,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -8907,7 +8907,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -8917,14 +8917,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -8941,7 +8941,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -8958,7 +8958,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -8968,14 +8968,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -9009,7 +9009,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -9019,14 +9019,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -9043,7 +9043,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -9060,7 +9060,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -9111,7 +9111,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -9128,7 +9128,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -9138,14 +9138,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -9162,7 +9162,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -9172,14 +9172,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -9189,14 +9189,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -9213,7 +9213,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -9230,7 +9230,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -9247,7 +9247,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -9264,7 +9264,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -9274,14 +9274,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -9298,7 +9298,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -9315,7 +9315,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -9332,7 +9332,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -9349,7 +9349,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -9366,7 +9366,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -9400,7 +9400,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -9410,14 +9410,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -9427,14 +9427,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -9444,14 +9444,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -9461,14 +9461,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -9478,14 +9478,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -9495,14 +9495,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -9512,14 +9512,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -9529,14 +9529,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -9553,7 +9553,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -9570,7 +9570,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9597,14 +9597,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -9621,7 +9621,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -9672,7 +9672,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -9682,14 +9682,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -9706,7 +9706,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -9716,14 +9716,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -9733,14 +9733,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -9750,14 +9750,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -9767,14 +9767,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -9791,7 +9791,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -9801,14 +9801,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -9818,14 +9818,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -9835,14 +9835,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -9852,14 +9852,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -9869,14 +9869,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9910,7 +9910,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -9920,14 +9920,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -9937,14 +9937,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -9954,14 +9954,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -9978,7 +9978,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -9988,14 +9988,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -10012,7 +10012,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -10029,7 +10029,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -10039,14 +10039,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -10056,14 +10056,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -10080,7 +10080,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -10090,14 +10090,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -10114,7 +10114,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -10131,7 +10131,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -10148,7 +10148,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -10158,14 +10158,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -10182,7 +10182,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -10192,14 +10192,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -10209,14 +10209,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -10233,7 +10233,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -10250,7 +10250,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -10260,14 +10260,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -10277,14 +10277,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -10301,7 +10301,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -10318,7 +10318,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -10335,7 +10335,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10345,14 +10345,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -10369,7 +10369,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -10379,14 +10379,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -10396,14 +10396,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -10413,14 +10413,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -10430,14 +10430,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -10454,7 +10454,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -10464,14 +10464,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -10488,7 +10488,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -10498,14 +10498,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -10522,7 +10522,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -10556,7 +10556,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -10590,7 +10590,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -10600,14 +10600,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -10617,14 +10617,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -10658,7 +10658,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -10668,14 +10668,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -10685,14 +10685,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -10702,14 +10702,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -10719,14 +10719,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -10743,7 +10743,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -10760,7 +10760,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -10777,7 +10777,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -10794,7 +10794,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -10811,7 +10811,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -10828,7 +10828,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10872,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10889,14 +10889,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -10913,7 +10913,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -10923,14 +10923,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -10940,14 +10940,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -10964,7 +10964,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -10974,14 +10974,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -10998,7 +10998,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -11015,7 +11015,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -11032,7 +11032,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -11049,7 +11049,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -11066,7 +11066,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -11083,7 +11083,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -11100,7 +11100,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -11110,14 +11110,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -11134,7 +11134,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -11151,7 +11151,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -11161,14 +11161,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -11178,14 +11178,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -11195,14 +11195,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -11219,7 +11219,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -11229,14 +11229,14 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -11253,7 +11253,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -11263,14 +11263,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -11280,14 +11280,14 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -11304,7 +11304,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -11321,7 +11321,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -11338,7 +11338,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -11355,7 +11355,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -11372,7 +11372,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -11389,7 +11389,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -11406,7 +11406,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -11423,7 +11423,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -11440,7 +11440,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -11457,7 +11457,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -11474,7 +11474,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -11491,7 +11491,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -11508,7 +11508,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -11525,7 +11525,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -11542,7 +11542,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -11559,7 +11559,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -11576,7 +11576,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -11593,7 +11593,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -11603,14 +11603,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -11627,7 +11627,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -11644,7 +11644,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -11661,7 +11661,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -11678,7 +11678,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -11695,7 +11695,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -11712,7 +11712,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -11729,7 +11729,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -11746,7 +11746,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -11756,14 +11756,14 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -11780,7 +11780,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -11797,7 +11797,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -11807,14 +11807,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -11831,7 +11831,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -11848,7 +11848,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -11858,14 +11858,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -11875,14 +11875,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -11899,7 +11899,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -11909,14 +11909,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -11926,14 +11926,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -11943,14 +11943,14 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -11960,14 +11960,14 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -11984,7 +11984,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -12001,7 +12001,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -12011,14 +12011,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -12035,7 +12035,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -12045,14 +12045,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -12077,356 +12077,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Banca Profilo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0001073045</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-04-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.153999999165535</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>4.545454570084565</v>
-      </c>
-      <c r="I2" t="n">
-        <v>33</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0004329733</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-05-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2.575000047683716</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>6.990291132690076</v>
-      </c>
-      <c r="I3" t="n">
-        <v>61</v>
-      </c>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ENAV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0005176406</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5.179999828338623</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>5.59845578398429</v>
-      </c>
-      <c r="I4" t="n">
-        <v>89</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>FOPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT0005203424</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>37.59999847412109</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>2.925532033617224</v>
-      </c>
-      <c r="I5" t="n">
-        <v>40</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>OMER S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IT0005453748</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>3.509999990463257</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>4.843304856464204</v>
-      </c>
-      <c r="I6" t="n">
-        <v>54</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RCS MediaGroup S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IT0004931496</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.9399999976158142</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>7.446808529526145</v>
-      </c>
-      <c r="I7" t="n">
-        <v>54</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SABAF S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>IT0001042610</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-05-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>4.461538461538462</v>
-      </c>
-      <c r="I8" t="n">
-        <v>61</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12437,911 +12090,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AEDES S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ASCOPIAVE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Altea Green Power S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Aquafil S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BANCA IFIS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>BANCA SISTEMA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>BIESSE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Banca Profilo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CULTI Milano S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CY4Gate S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Cloudia Research S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DATALOGIC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>DIGITAL BROS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>EL.EN. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>ELICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>EMAK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>EUROTECH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>F.I.L.A. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Fiera Milano S.p.A</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>IGD SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>IRCE s.p.a</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>ITALMOBILIARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Impianti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>MARR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Matica Fintec S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Monnalisa S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>NEWPRINCES</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>OMER S.p.A.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>OSAI Automation System S.p.A.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Orsero S.p.A.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>POWERSOFT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>REVO Insurance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SABAF S.p.A.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>SECO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SOGEFI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SOGEFI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Smart Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>UNIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>VALSOIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>